--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/oct-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1018,7 +1018,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2268-145-CM26</t>
+          <t>1469-2995-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1043,37 +1043,41 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.802.163-5</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>15260.84</v>
+        <v>20090.88</v>
       </c>
     </row>
     <row r="11">
@@ -1140,7 +1144,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1469-2995-CM26</t>
+          <t>2268-145-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1165,41 +1169,37 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.802.163-5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>20090.88</v>
+        <v>15260.84</v>
       </c>
     </row>
     <row r="13">
@@ -1587,7 +1587,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057414-652-CM26</t>
+          <t>1216094-64-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1612,47 +1612,43 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>66920.25</v>
+        <v>60966.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1075963-13455-CM26</t>
+          <t>1425525-35-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1677,47 +1673,43 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.560-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.444.489-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>50944.95</v>
+        <v>46803.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>709603-204-SE26</t>
+          <t>1075963-13455-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1742,27 +1734,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.980.220-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1776,13 +1768,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27333.53</v>
+        <v>50944.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1425525-35-CM26</t>
+          <t>1057414-652-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1807,43 +1799,47 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>62.000.560-6</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>46803.45</v>
+        <v>66920.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1216094-64-CM26</t>
+          <t>709603-204-SE26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1868,12 +1864,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1883,22 +1879,26 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>60966.87</v>
+        <v>27333.53</v>
       </c>
     </row>
     <row r="24">
@@ -2091,7 +2091,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4202-43-CM26</t>
+          <t>4452-737-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2116,27 +2116,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>INFO WORLD SA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>96.532.020-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2146,13 +2146,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>52188.84</v>
+        <v>70387.38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4452-737-CM26</t>
+          <t>5768-135-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2177,27 +2177,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INFO WORLD SA</t>
+          <t>Inteldata Ltda.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.532.020-2</t>
+          <t>76.414.840-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>70387.38</v>
+        <v>25209.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5768-135-CM26</t>
+          <t>4202-43-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Inteldata Ltda.</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.414.840-1</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>25209.84</v>
+        <v>52188.84</v>
       </c>
     </row>
     <row r="30">
@@ -2643,6 +2643,258 @@
       </c>
       <c r="M35" s="2" t="n">
         <v>39161.57</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2785-755-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.264.800-5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>18303.93</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>584105-247-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.979.830-9</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE ENERGIA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>LIVISTER CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.622.841-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>449484.49</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5067-2527-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>60.911.000-7</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.528.848-7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>7179.18</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1057547-15634-SE26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>17302.97</v>
       </c>
     </row>
   </sheetData>
